--- a/public/outils/matrices/chiffrage-de-travaux-par-lot.xlsx
+++ b/public/outils/matrices/chiffrage-de-travaux-par-lot.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="568">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -51,7 +51,7 @@
     <t>Il part de cinq données du bien (surface, niveaux, hauteur sous plafond, façades exposées, part rénovée), en déduit la géométrie, chiffre vingt-huit postes en quantité × prix unitaire, le prix étant pris dans une fourchette de marché selon un curseur, ajoute aléas et honoraires, calcule la TVA ligne à ligne à trois taux, et qualifie le chantier au regard de la règle de l'immeuble rendu neuf. Il rend trois budgets : bas de fourchette, retenu, haut de fourchette.</t>
   </si>
   <si>
-    <t>Vous remplissez les cellules bleues de haut en bas ; à mesure que les devis arrivent, vous forcez les quantités et les prix, et la fourchette se referme. Deux mots reviennent partout : le gros œuvre, ce qui tient le bâtiment (fondations, murs porteurs, planchers porteurs, charpente), et le second œuvre, tout ce qui vient ensuite (cloisons, fenêtres, plomberie, électricité, chauffage, finitions).</t>
+    <t>Vous remplissez les cellules violettes de haut en bas ; à mesure que les devis arrivent, vous forcez les quantités et les prix, et la fourchette se referme. Deux mots reviennent partout : le gros œuvre, ce qui tient le bâtiment (fondations, murs porteurs, planchers porteurs, charpente), et le second œuvre, tout ce qui vient ensuite (cloisons, fenêtres, plomberie, électricité, chauffage, finitions).</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -153,13 +153,13 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu clair</t>
+    <t>Fond violet clair</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
   </si>
   <si>
-    <t>Vous la remplissez, ou vous l'effacez avec la touche Suppr, même feuille protégée. Jamais de formule dedans. Dans le tableau, une cellule bleue vide laisse l'automatisme.</t>
+    <t>Vous la remplissez, ou vous l'effacez avec la touche Suppr, même feuille protégée. Jamais de formule dedans. Dans le tableau, une cellule violette vide laisse l'automatisme.</t>
   </si>
   <si>
     <t>Fond blanc</t>
@@ -171,7 +171,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond bleu pâle, gras</t>
+    <t>Fond violet pâle, gras</t>
   </si>
   <si>
     <t>Résultat de bloc, chiffre clé</t>
@@ -180,7 +180,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section, en-tête de tableau</t>
@@ -207,7 +207,7 @@
     <t>Rouge, la cellule affiche « À CORRIGER » : corrigez la saisie indiquée par le commentaire à droite. Le récapitulatif reste vide tant qu'un contrôle bloquant est rouge.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Pour modifier une cellule blanche : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé. En pratique, tout ce qu'un professionnel doit régler est bleu, dans le Chiffrage ou dans le Référentiel.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Pour modifier une cellule blanche : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé. En pratique, tout ce qu'un professionnel doit régler est violet, dans le Chiffrage ou dans le Référentiel.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -228,7 +228,7 @@
     <t>Chiffrage!D7:D16, F29:F59 et J29:J59, D62:D77</t>
   </si>
   <si>
-    <t>Le classeur est livré rempli d'un exemple (appartement de 90 m², détaillé plus bas). Gardez-le pour vous repérer, ou effacez toutes les cellules bleues du Chiffrage avant de saisir votre dossier : sélectionnez-les et appuyez sur Suppr, la protection de la feuille ne s'y oppose pas. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être chez vous : les 8 quantités forcées de la colonne F (dont les 6 zéros qui désactivent couverture, charpente, combles, chaudière, ravalement et VRD, la voirie et les réseaux du terrain), les douze réponses du bloc TVA, le taux forcé D77 (à laisser vide) et le curseur D14.</t>
+    <t>Le classeur est livré rempli d'un exemple (appartement de 90 m², détaillé plus bas). Gardez-le pour vous repérer, ou effacez toutes les cellules violettes du Chiffrage avant de saisir votre dossier : sélectionnez-les et appuyez sur Suppr, la protection de la feuille ne s'y oppose pas. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être chez vous : les 8 quantités forcées de la colonne F (dont les 6 zéros qui désactivent couverture, charpente, combles, chaudière, ravalement et VRD, la voirie et les réseaux du terrain), les douze réponses du bloc TVA, le taux forcé D77 (à laisser vide) et le curseur D14.</t>
   </si>
   <si>
     <t>Une saisie résiduelle de l'exemple est l'erreur la plus probable d'un premier usage : sur une maison, les trois zéros hérités de l'appartement (couverture, charpente, combles) font disparaître 15 030 € de travaux sans un mot.</t>
@@ -276,7 +276,7 @@
     <t>Chiffrage!F29:F59 et J29:J59</t>
   </si>
   <si>
-    <t>Deux colonnes bleues seulement, F (quantité forcée) et J (prix forcé) : les autres sont calculées. Quantité forcée : 0 pour désactiver un poste (couverture, charpente, combles, chaudière, ravalement et VRD sont livrés à 0 pour un appartement), une valeur comptée sur plan sinon, vide pour l'automatisme. Prix forcés à mesure que les devis arrivent, en priorité sur pompe à chaleur, cuisine, salle de bains, ventilation.</t>
+    <t>Deux colonnes violettes seulement, F (quantité forcée) et J (prix forcé) : les autres sont calculées. Quantité forcée : 0 pour désactiver un poste (couverture, charpente, combles, chaudière, ravalement et VRD sont livrés à 0 pour un appartement), une valeur comptée sur plan sinon, vide pour l'automatisme. Prix forcés à mesure que les devis arrivent, en priorité sur pompe à chaleur, cuisine, salle de bains, ventilation.</t>
   </si>
   <si>
     <t>Une valeur forcée l'emporte toujours sur le calcul sans le détruire. Un prix forcé vaut dans les trois colonnes du récapitulatif : c'est un devis.</t>
@@ -432,7 +432,7 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les barèmes et les repères (taux de TVA, seuils de l'immeuble neuf, fourchettes de prix, bandes par famille, repères au m²) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée dans le Référentiel. Les données de projet (surface, niveaux, façades, curseur, quantités et prix forcés, réponses du bloc TVA) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les barèmes et les repères (taux de TVA, seuils de l'immeuble neuf, fourchettes de prix, bandes par famille, repères au m²) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée dans le Référentiel. Les données de projet (surface, niveaux, façades, curseur, quantités et prix forcés, réponses du bloc TVA) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
     <t>Une seule date commande tout, Référentiel!C109 : chaque mention « Vérifié le » du Référentiel et de Méthode la lit, vous n'avez donc qu'une cellule à corriger. En revanche, les chiffres cités en toutes lettres dans ce guide et dans Méthode (repères au m², fourchettes de curseur, d'aléas et d'honoraires, montants de l'exemple) sont du texte, millésime 2026 : relisez-les à chaque mise à jour du Référentiel, ils ne se recalculent pas.</t>
@@ -654,7 +654,7 @@
     <t>Cinq entrées, vingt-huit postes chiffrés en fourchette, chaque quantité et chaque prix restent forçables, et la TVA du chantier est qualifiée.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  LE BIEN</t>
@@ -1044,13 +1044,13 @@
     <t>Un prix, un taux de TVA et un ratio par prestation ; les barèmes et les conventions du classeur. Rien n'est écrit en dur ailleurs.</t>
   </si>
   <si>
-    <t>Fourchettes indicatives 2026, France hors Paris intra-muros. Fournitures et pose, hors taxes. Les cellules bleues sont vos prix : confrontez-les à vos trois derniers chantiers.</t>
+    <t>Fourchettes indicatives 2026, France hors Paris intra-muros. Fournitures et pose, hors taxes. Les cellules violettes sont vos prix : confrontez-les à vos trois derniers chantiers.</t>
   </si>
   <si>
     <t>Référentiel cohérent (bornes des barèmes, des prix, des ratios et des taux)</t>
   </si>
   <si>
-    <t>Rouge : une cellule bleue de cet onglet manque ou sort de ses bornes. Le Chiffrage le reprend et suspend son récapitulatif.</t>
+    <t>Rouge : une cellule violette de cet onglet manque ou sort de ses bornes. Le Chiffrage le reprend et suspend son récapitulatif.</t>
   </si>
   <si>
     <t xml:space="preserve">  BARÈMES RÉGLEMENTAIRES : TVA DES TRAVAUX ET IMMEUBLE RENDU NEUF (DROIT 2026)</t>
@@ -1602,7 +1602,7 @@
     <t>Quantité et prix forcés</t>
   </si>
   <si>
-    <t>Une valeur saisie dans une colonne bleue l'emporte toujours sur le calcul, sans le détruire : effacez-la et l'automatisme revient. C'est la colonne à remplir à mesure que les devis arrivent. Saisir 0 en quantité forcée désactive le poste.</t>
+    <t>Une valeur saisie dans une colonne violette l'emporte toujours sur le calcul, sans le détruire : effacez-la et l'automatisme revient. C'est la colonne à remplir à mesure que les devis arrivent. Saisir 0 en quantité forcée désactive le poste.</t>
   </si>
   <si>
     <t>Géométrie</t>
@@ -1769,7 +1769,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1789,19 +1789,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1813,7 +1813,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1826,12 +1826,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1841,7 +1841,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2273,6 +2273,138 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11706225" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11706225" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="16630650" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16630650" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8382000" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8382000" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3549,13 +3681,14 @@
     <mergeCell ref="C12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:N112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6315,6 +6448,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -6345,7 +6479,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFB08C4E"/>
+    <tabColor rgb="FF495669"/>
   </sheetPr>
   <dimension ref="B1:K111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8342,13 +8476,14 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8780,5 +8915,6 @@
     <mergeCell ref="B25:C25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>